--- a/02_DIA_inicio_2026_analisis_assets/rbd_9431_escuela-villa-san-miguel_nt2_rubricas.xlsx
+++ b/02_DIA_inicio_2026_analisis_assets/rbd_9431_escuela-villa-san-miguel_nt2_rubricas.xlsx
@@ -1992,13 +1992,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{64C8C962-F86B-47B1-A99D-A991ECED2156}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{740A8B71-50F4-4182-A39F-09397EDFF3A8}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{ECF917BD-1DAC-43DD-B880-CDCA3E87E2D3}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{13989003-3575-4DED-ADAA-9658F842672B}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{75DC76DC-CB2B-4C0F-9ACE-DBC0A8008B7B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EC95E99A-849E-49B4-83E3-9A1B7EB57A45}"/>
 </file>